--- a/etf_holdings/2026-09-17_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-17_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,52 +950,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6213</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>聯茂</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1.66%</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>1.74%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1147000</v>
+      </c>
       <c r="K10" t="n">
-        <v>170000</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>1197000</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-16_00982A_full_holdings.xlsx</t>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1005,60 +1023,60 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>819000</v>
+        <v>114000</v>
       </c>
       <c r="K11" t="n">
-        <v>820000</v>
+        <v>108000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-16_00982A_full_holdings.xlsx</t>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1068,60 +1086,60 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.77%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>863000</v>
+        <v>327000</v>
       </c>
       <c r="K12" t="n">
-        <v>790000</v>
+        <v>348000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-73,000</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-16_00982A_full_holdings.xlsx</t>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1131,60 +1149,60 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5.59%</t>
+          <t>3.01%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.99%</t>
+          <t>3.01%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1171225</v>
+        <v>304000</v>
       </c>
       <c r="K13" t="n">
-        <v>1136225</v>
+        <v>305000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-35,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-16_00982A_full_holdings.xlsx</t>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1194,60 +1212,60 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>45000</v>
+        <v>52000</v>
       </c>
       <c r="K14" t="n">
-        <v>55000</v>
+        <v>46000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-09-16_00403A_full_holdings.xlsx</t>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1262,55 +1280,55 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>弘塑科技</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>弘塑科技</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5.20%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5.71%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>55000000</v>
+        <v>22000</v>
       </c>
       <c r="K15" t="n">
-        <v>58000000</v>
+        <v>24000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-09-16_00403A_full_holdings.xlsx</t>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1320,60 +1338,60 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>2.24%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>760000</v>
+        <v>273000</v>
       </c>
       <c r="K16" t="n">
-        <v>1200000</v>
+        <v>266000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>440,000</t>
+          <t>-7,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-09-16_00403A_full_holdings.xlsx</t>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1383,60 +1401,60 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>380000</v>
+        <v>564000</v>
       </c>
       <c r="K17" t="n">
-        <v>280000</v>
+        <v>574000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-100,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-09-16_00403A_full_holdings.xlsx</t>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1446,60 +1464,60 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1102000</v>
+        <v>104000</v>
       </c>
       <c r="K18" t="n">
-        <v>1300000</v>
+        <v>99000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>198,000</t>
+          <t>-5,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-09-16_00403A_full_holdings.xlsx</t>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1509,53 +1527,53 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>160000</v>
+        <v>386000</v>
       </c>
       <c r="K19" t="n">
-        <v>120000</v>
+        <v>388000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-40,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-09-16_00403A_full_holdings.xlsx</t>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1577,43 +1595,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1147000</v>
+        <v>368000</v>
       </c>
       <c r="K20" t="n">
-        <v>1197000</v>
+        <v>378000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1635,48 +1653,48 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>台達電子</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>台達電子</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>4.31%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>4.43%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>114000</v>
+        <v>76000</v>
       </c>
       <c r="K21" t="n">
-        <v>108000</v>
+        <v>77000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1698,48 +1716,48 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>2.66%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>327000</v>
+        <v>191000</v>
       </c>
       <c r="K22" t="n">
-        <v>348000</v>
+        <v>183000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>-8,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1766,43 +1784,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>304000</v>
+        <v>16000</v>
       </c>
       <c r="K23" t="n">
-        <v>305000</v>
+        <v>18000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1824,48 +1842,48 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>52000</v>
+        <v>71000</v>
       </c>
       <c r="K24" t="n">
-        <v>46000</v>
+        <v>75000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1892,43 +1910,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>弘塑科技</t>
+          <t>金居開發</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>弘塑科技</t>
+          <t>金居開發</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>22000</v>
+        <v>108000</v>
       </c>
       <c r="K25" t="n">
-        <v>24000</v>
+        <v>121000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1940,322 +1958,232 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>景碩科技</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>景碩科技</t>
-        </is>
-      </c>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.26%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2.24%</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>273000</v>
-      </c>
-      <c r="K26" t="n">
-        <v>266000</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>-7,000</t>
-        </is>
-      </c>
+        <v>200000</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+          <t>2026-09-16_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>欣銓</t>
-        </is>
-      </c>
+          <t>世界先進</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.30%</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>1.31%</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
+          <t>0.77%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>564000</v>
-      </c>
-      <c r="K27" t="n">
-        <v>574000</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
+        <v>1351000</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+          <t>2026-09-16_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
+          <t>台 燿</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2.03%</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>-0.12%</t>
-        </is>
-      </c>
+          <t>0.89%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>104000</v>
-      </c>
-      <c r="K28" t="n">
-        <v>99000</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>-5,000</t>
-        </is>
-      </c>
+        <v>175000</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+          <t>2026-09-16_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.92%</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>1.97%</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>+0.05%</t>
-        </is>
-      </c>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>386000</v>
-      </c>
-      <c r="K29" t="n">
-        <v>388000</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
+        <v>21000</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+          <t>2026-09-16_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>頎邦</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>頎邦</t>
-        </is>
-      </c>
+          <t>宏全</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.77%</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>0.81%</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>+0.04%</t>
-        </is>
-      </c>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>368000</v>
-      </c>
-      <c r="K30" t="n">
-        <v>378000</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
+        <v>180000</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+          <t>2026-09-16_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2270,55 +2198,55 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4.31%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.43%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>76000</v>
+        <v>1861000</v>
       </c>
       <c r="K31" t="n">
-        <v>77000</v>
+        <v>3041000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,180,000</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+          <t>2026-09-16_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2333,55 +2261,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>191000</v>
+        <v>6267040</v>
       </c>
       <c r="K32" t="n">
-        <v>183000</v>
+        <v>2241040</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-8,000</t>
+          <t>-4,026,000</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+          <t>2026-09-16_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2396,55 +2324,55 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.57%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>16000</v>
+        <v>1532000</v>
       </c>
       <c r="K33" t="n">
-        <v>18000</v>
+        <v>2208000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>676,000</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+          <t>2026-09-16_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2459,586 +2387,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>71000</v>
+        <v>3309000</v>
       </c>
       <c r="K34" t="n">
-        <v>75000</v>
+        <v>4903000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>1,594,000</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
-        <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>金居開發</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>金居開發</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>0.54%</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>0.63%</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>+0.09%</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>108000</v>
-      </c>
-      <c r="K35" t="n">
-        <v>121000</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>13,000</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>1215</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>卜蜂</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>0.08%</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="n">
-        <v>200000</v>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>2026-09-16_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>5347</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>世界先進</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0.77%</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="n">
-        <v>1351000</v>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2026-09-16_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>台 燿</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>0.89%</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
-        <v>175000</v>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>2026-09-16_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>0.47%</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="n">
-        <v>21000</v>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2026-09-16_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>9939</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>宏全</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>0.08%</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="n">
-        <v>180000</v>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-09-16_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>1.50%</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2.58%</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>+1.08%</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>1861000</v>
-      </c>
-      <c r="K41" t="n">
-        <v>3041000</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>1,180,000</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2026-09-16_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>1.57%</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>0.56%</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>-1.01%</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>6267040</v>
-      </c>
-      <c r="K42" t="n">
-        <v>2241040</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>-4,026,000</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>2026-09-16_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>文曄</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>文曄</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>1.05%</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>1.62%</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>+0.57%</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>1532000</v>
-      </c>
-      <c r="K43" t="n">
-        <v>2208000</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>676,000</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-09-16_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>1.52%</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>+0.56%</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>3309000</v>
-      </c>
-      <c r="K44" t="n">
-        <v>4903000</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>1,594,000</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
         <is>
           <t>2026-09-16_00400A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-09-17_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-17_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,70 +950,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2303</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
+          <t>6213</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1.66%</t>
-        </is>
-      </c>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.74%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>+0.08%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>1147000</v>
-      </c>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>1197000</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>50,000</t>
-        </is>
-      </c>
+        <v>170000</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+          <t>2026-09-16_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1023,60 +1005,60 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>台達電子</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>台達電子</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>3.51%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>3.48%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>114000</v>
+        <v>819000</v>
       </c>
       <c r="K11" t="n">
-        <v>108000</v>
+        <v>820000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+          <t>2026-09-16_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1086,60 +1068,60 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>327000</v>
+        <v>863000</v>
       </c>
       <c r="K12" t="n">
-        <v>348000</v>
+        <v>790000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>-73,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+          <t>2026-09-16_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1149,60 +1131,60 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>5.59%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>4.99%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>304000</v>
+        <v>1171225</v>
       </c>
       <c r="K13" t="n">
-        <v>305000</v>
+        <v>1136225</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>-35,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+          <t>2026-09-16_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1212,60 +1194,60 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>52000</v>
+        <v>45000</v>
       </c>
       <c r="K14" t="n">
-        <v>46000</v>
+        <v>55000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+          <t>2026-09-16_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1280,55 +1262,55 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>弘塑科技</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>弘塑科技</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>5.20%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>5.71%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>22000</v>
+        <v>55000000</v>
       </c>
       <c r="K15" t="n">
-        <v>24000</v>
+        <v>58000000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+          <t>2026-09-16_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1338,60 +1320,60 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>273000</v>
+        <v>760000</v>
       </c>
       <c r="K16" t="n">
-        <v>266000</v>
+        <v>1200000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-7,000</t>
+          <t>440,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+          <t>2026-09-16_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1401,60 +1383,60 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>564000</v>
+        <v>380000</v>
       </c>
       <c r="K17" t="n">
-        <v>574000</v>
+        <v>280000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>-100,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+          <t>2026-09-16_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1464,60 +1446,60 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>104000</v>
+        <v>1102000</v>
       </c>
       <c r="K18" t="n">
-        <v>99000</v>
+        <v>1300000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-5,000</t>
+          <t>198,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+          <t>2026-09-16_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1527,53 +1509,53 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>386000</v>
+        <v>160000</v>
       </c>
       <c r="K19" t="n">
-        <v>388000</v>
+        <v>120000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>-40,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+          <t>2026-09-16_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1595,43 +1577,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>368000</v>
+        <v>1147000</v>
       </c>
       <c r="K20" t="n">
-        <v>378000</v>
+        <v>1197000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1653,48 +1635,48 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4.31%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.43%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>76000</v>
+        <v>114000</v>
       </c>
       <c r="K21" t="n">
-        <v>77000</v>
+        <v>108000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1716,48 +1698,48 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>1.77%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>191000</v>
+        <v>327000</v>
       </c>
       <c r="K22" t="n">
-        <v>183000</v>
+        <v>348000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-8,000</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1784,43 +1766,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>3.01%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>3.01%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>16000</v>
+        <v>304000</v>
       </c>
       <c r="K23" t="n">
-        <v>18000</v>
+        <v>305000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1842,48 +1824,48 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>71000</v>
+        <v>52000</v>
       </c>
       <c r="K24" t="n">
-        <v>75000</v>
+        <v>46000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1910,43 +1892,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>金居開發</t>
+          <t>弘塑科技</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>金居開發</t>
+          <t>弘塑科技</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>108000</v>
+        <v>22000</v>
       </c>
       <c r="K25" t="n">
-        <v>121000</v>
+        <v>24000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1958,232 +1940,322 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>卜蜂</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.08%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2.24%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
       <c r="J26" t="n">
-        <v>200000</v>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+        <v>273000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>266000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-7,000</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-16_00400A_full_holdings.xlsx</t>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>世界先進</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.77%</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1.31%</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
       <c r="J27" t="n">
-        <v>1351000</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+        <v>564000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>574000</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-16_00400A_full_holdings.xlsx</t>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>台 燿</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.89%</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+          <t>2.15%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2.03%</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
       <c r="J28" t="n">
-        <v>175000</v>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+        <v>104000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>99000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-5,000</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-16_00400A_full_holdings.xlsx</t>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.47%</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+          <t>1.92%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1.97%</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
       <c r="J29" t="n">
-        <v>21000</v>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+        <v>386000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>388000</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-16_00400A_full_holdings.xlsx</t>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>宏全</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.08%</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+          <t>0.77%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0.81%</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
       <c r="J30" t="n">
-        <v>180000</v>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+        <v>368000</v>
+      </c>
+      <c r="K30" t="n">
+        <v>378000</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-09-16_00400A_full_holdings.xlsx</t>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2198,55 +2270,55 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>4.31%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>4.43%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>1861000</v>
+        <v>76000</v>
       </c>
       <c r="K31" t="n">
-        <v>3041000</v>
+        <v>77000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1,180,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-09-16_00400A_full_holdings.xlsx</t>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2261,55 +2333,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>2.66%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>6267040</v>
+        <v>191000</v>
       </c>
       <c r="K32" t="n">
-        <v>2241040</v>
+        <v>183000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-4,026,000</t>
+          <t>-8,000</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09-16_00400A_full_holdings.xlsx</t>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2324,109 +2396,649 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>+0.57%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>1532000</v>
+        <v>16000</v>
       </c>
       <c r="K33" t="n">
-        <v>2208000</v>
+        <v>18000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>676,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-16_00400A_full_holdings.xlsx</t>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1.50%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>71000</v>
+      </c>
+      <c r="K34" t="n">
+        <v>75000</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8358</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>金居開發</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>金居開發</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>+0.09%</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>108000</v>
+      </c>
+      <c r="K35" t="n">
+        <v>121000</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>13,000</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09-16_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>00400A</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="n">
+        <v>200000</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09-16_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>世界先進</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.77%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="n">
+        <v>1351000</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09-16_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>台 燿</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0.89%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>175000</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09-16_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>21000</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09-16_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>9939</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>宏全</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>180000</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-09-16_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1.50%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2.58%</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>+1.08%</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>1861000</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3041000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1,180,000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-09-16_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>-1.01%</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>6267040</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2241040</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>-4,026,000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-09-16_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3036</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>文曄</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>文曄</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1.05%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1.62%</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>+0.57%</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>1532000</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2208000</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>676,000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-09-16_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>6505</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>台塑化</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>台塑化</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>0.96%</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>1.52%</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>+0.56%</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="J44" t="n">
         <v>3309000</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K44" t="n">
         <v>4903000</v>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>1,594,000</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>2026-09-16_00400A_full_holdings.xlsx</t>
         </is>
